--- a/LV_Regulator/LV_Regulator/Manufacture/LV_Regulator_BoM.xlsx
+++ b/LV_Regulator/LV_Regulator/Manufacture/LV_Regulator_BoM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pyonier\Documents\GitHub\LVPSU\LV_Regulator\LV_Regulator\Manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42A18F3B-B579-4CF1-87BD-B584EFF01452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E079B17-3171-4FE8-9732-F7D74E03EC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B4049184-6425-4836-AF0C-0336DDFBEC93}"/>
   </bookViews>
@@ -211,12 +211,6 @@
     <t>56uF</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/CC1206JRNPO0BN560/5884457?s=N4IgTCBcDaIMJwIxgAwDYBSAlAcgBQHkUAhHAVjRRAF0BfIA</t>
-  </si>
-  <si>
-    <t>https://eu.mouser.com/ProductDetail/YAGEO/CC1206JRNPO0BN560?qs=AgBp2OyFlx%252BW%2FnaeCGBiHg%3D%3D</t>
-  </si>
-  <si>
     <t>C32, C33</t>
   </si>
   <si>
@@ -854,6 +848,12 @@
   </si>
   <si>
     <t>https://eu.mouser.com/ProductDetail/ECS/ECS-80-8-30-JGN-TR?qs=rQFj71Wb1eX34%2FP%2F%2Fw8%2FDA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Eaton-Electronics/EHBSA080M5601010T?qs=sGAEpiMZZMsh%252B1woXyUXjyUUqvU%2FlejKTQ9mdTwBEYY%3D</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/eaton-electronics-division/EHBSA080M5601010T/26408296?s=N4IgTCBcDaIKIAkBCBlAggBgBwYLIFYA2DARlIwBUQBdAXyA</t>
   </si>
 </sst>
 </file>
@@ -1697,6 +1697,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9665A2A8-71E5-4C81-B45D-479E88EB3CEB}">
   <dimension ref="A1:G83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="161.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="136" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2103,10 +2107,10 @@
         <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>277</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2114,10 +2118,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2126,10 +2130,10 @@
         <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2137,7 +2141,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
         <v>61</v>
@@ -2146,13 +2150,13 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" t="s">
         <v>70</v>
-      </c>
-      <c r="F20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2160,10 +2164,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2172,10 +2176,10 @@
         <v>430450400</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2183,22 +2187,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
         <v>77</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
         <v>78</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>79</v>
-      </c>
-      <c r="F22" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2206,22 +2210,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" t="s">
         <v>84</v>
-      </c>
-      <c r="F23" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2229,16 +2233,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -2252,10 +2256,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2264,10 +2268,10 @@
         <v>2169890001</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2275,7 +2279,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -2284,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
@@ -2298,22 +2302,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
         <v>95</v>
       </c>
-      <c r="C27" t="s">
+      <c r="F27" t="s">
         <v>96</v>
       </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>97</v>
-      </c>
-      <c r="F27" t="s">
-        <v>98</v>
-      </c>
-      <c r="G27" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2321,22 +2325,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" t="s">
         <v>100</v>
       </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>101</v>
-      </c>
-      <c r="F28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G28" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2344,22 +2348,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" t="s">
         <v>105</v>
-      </c>
-      <c r="F29" t="s">
-        <v>106</v>
-      </c>
-      <c r="G29" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2367,22 +2371,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
         <v>108</v>
       </c>
-      <c r="C30" t="s">
+      <c r="F30" t="s">
         <v>109</v>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>110</v>
-      </c>
-      <c r="F30" t="s">
-        <v>111</v>
-      </c>
-      <c r="G30" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2390,22 +2394,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G31" t="s">
         <v>114</v>
-      </c>
-      <c r="F31" t="s">
-        <v>115</v>
-      </c>
-      <c r="G31" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2413,10 +2417,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -2425,10 +2429,10 @@
         <v>430450800</v>
       </c>
       <c r="F32" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2436,7 +2440,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
@@ -2445,13 +2449,13 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" t="s">
         <v>122</v>
-      </c>
-      <c r="F33" t="s">
-        <v>123</v>
-      </c>
-      <c r="G33" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2459,7 +2463,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C34" s="1">
         <v>415000000000</v>
@@ -2468,13 +2472,13 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2482,22 +2486,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
         <v>127</v>
       </c>
-      <c r="C35" t="s">
+      <c r="F35" t="s">
         <v>128</v>
       </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>129</v>
-      </c>
-      <c r="F35" t="s">
-        <v>130</v>
-      </c>
-      <c r="G35" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2505,7 +2509,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
@@ -2514,13 +2518,13 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2528,22 +2532,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
         <v>134</v>
       </c>
-      <c r="C37" t="s">
+      <c r="F37" t="s">
         <v>135</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>136</v>
-      </c>
-      <c r="F37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2551,22 +2555,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D38">
         <v>9</v>
       </c>
       <c r="E38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38" t="s">
         <v>141</v>
-      </c>
-      <c r="F38" t="s">
-        <v>142</v>
-      </c>
-      <c r="G38" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2574,10 +2578,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2586,10 +2590,10 @@
         <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2597,22 +2601,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" t="s">
         <v>146</v>
       </c>
-      <c r="C40" t="s">
-        <v>140</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>147</v>
-      </c>
-      <c r="F40" t="s">
-        <v>148</v>
-      </c>
-      <c r="G40" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2620,22 +2624,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F41" t="s">
         <v>150</v>
       </c>
-      <c r="C41" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="G41" t="s">
         <v>151</v>
-      </c>
-      <c r="F41" t="s">
-        <v>152</v>
-      </c>
-      <c r="G41" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2643,22 +2647,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F42" t="s">
+        <v>154</v>
+      </c>
+      <c r="G42" t="s">
         <v>155</v>
-      </c>
-      <c r="F42" t="s">
-        <v>156</v>
-      </c>
-      <c r="G42" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2666,22 +2670,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>157</v>
+      </c>
+      <c r="F43" t="s">
         <v>158</v>
       </c>
-      <c r="C43" t="s">
-        <v>140</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>159</v>
-      </c>
-      <c r="F43" t="s">
-        <v>160</v>
-      </c>
-      <c r="G43" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2689,22 +2693,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D44">
         <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G44" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2712,10 +2716,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -2724,10 +2728,10 @@
         <v>270</v>
       </c>
       <c r="F45" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G45" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2735,10 +2739,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D46">
         <v>9</v>
@@ -2747,10 +2751,10 @@
         <v>130</v>
       </c>
       <c r="F46" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G46" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2758,22 +2762,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D47">
         <v>2</v>
       </c>
       <c r="E47" t="s">
+        <v>169</v>
+      </c>
+      <c r="F47" t="s">
+        <v>170</v>
+      </c>
+      <c r="G47" t="s">
         <v>171</v>
-      </c>
-      <c r="F47" t="s">
-        <v>172</v>
-      </c>
-      <c r="G47" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2781,22 +2785,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D48">
         <v>2</v>
       </c>
       <c r="E48" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48" t="s">
+        <v>174</v>
+      </c>
+      <c r="G48" t="s">
         <v>175</v>
-      </c>
-      <c r="F48" t="s">
-        <v>176</v>
-      </c>
-      <c r="G48" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2804,22 +2808,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>177</v>
+      </c>
+      <c r="F49" t="s">
         <v>178</v>
       </c>
-      <c r="C49" t="s">
-        <v>140</v>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="G49" t="s">
         <v>179</v>
-      </c>
-      <c r="F49" t="s">
-        <v>180</v>
-      </c>
-      <c r="G49" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2827,22 +2831,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>180</v>
+      </c>
+      <c r="C50" t="s">
+        <v>138</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
+        <v>181</v>
+      </c>
+      <c r="F50" t="s">
         <v>182</v>
       </c>
-      <c r="C50" t="s">
-        <v>140</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>183</v>
-      </c>
-      <c r="F50" t="s">
-        <v>184</v>
-      </c>
-      <c r="G50" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2850,22 +2854,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
+        <v>185</v>
+      </c>
+      <c r="F51" t="s">
         <v>186</v>
       </c>
-      <c r="C51" t="s">
-        <v>140</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="G51" t="s">
         <v>187</v>
-      </c>
-      <c r="F51" t="s">
-        <v>188</v>
-      </c>
-      <c r="G51" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2873,22 +2877,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" t="s">
+        <v>138</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>189</v>
+      </c>
+      <c r="F52" t="s">
         <v>190</v>
       </c>
-      <c r="C52" t="s">
-        <v>140</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>191</v>
-      </c>
-      <c r="F52" t="s">
-        <v>192</v>
-      </c>
-      <c r="G52" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2896,22 +2900,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>193</v>
+      </c>
+      <c r="F53" t="s">
         <v>194</v>
       </c>
-      <c r="C53" t="s">
-        <v>140</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>195</v>
-      </c>
-      <c r="F53" t="s">
-        <v>196</v>
-      </c>
-      <c r="G53" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2919,22 +2923,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54" t="s">
+        <v>197</v>
+      </c>
+      <c r="F54" t="s">
+        <v>198</v>
+      </c>
+      <c r="G54" t="s">
         <v>199</v>
-      </c>
-      <c r="F54" t="s">
-        <v>200</v>
-      </c>
-      <c r="G54" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2942,22 +2946,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>200</v>
+      </c>
+      <c r="C55" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>201</v>
+      </c>
+      <c r="F55" t="s">
         <v>202</v>
       </c>
-      <c r="C55" t="s">
-        <v>140</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>203</v>
-      </c>
-      <c r="F55" t="s">
-        <v>204</v>
-      </c>
-      <c r="G55" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2965,22 +2969,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C56" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D56">
         <v>2</v>
       </c>
       <c r="E56" t="s">
+        <v>205</v>
+      </c>
+      <c r="F56" t="s">
+        <v>206</v>
+      </c>
+      <c r="G56" t="s">
         <v>207</v>
-      </c>
-      <c r="F56" t="s">
-        <v>208</v>
-      </c>
-      <c r="G56" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2988,22 +2992,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D57">
         <v>2</v>
       </c>
       <c r="E57" t="s">
+        <v>209</v>
+      </c>
+      <c r="F57" t="s">
+        <v>210</v>
+      </c>
+      <c r="G57" t="s">
         <v>211</v>
-      </c>
-      <c r="F57" t="s">
-        <v>212</v>
-      </c>
-      <c r="G57" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3011,22 +3015,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>212</v>
+      </c>
+      <c r="C58" t="s">
+        <v>138</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>213</v>
+      </c>
+      <c r="F58" t="s">
         <v>214</v>
       </c>
-      <c r="C58" t="s">
-        <v>140</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>215</v>
-      </c>
-      <c r="F58" t="s">
-        <v>216</v>
-      </c>
-      <c r="G58" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3034,22 +3038,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>216</v>
+      </c>
+      <c r="C59" t="s">
+        <v>138</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>217</v>
+      </c>
+      <c r="F59" t="s">
         <v>218</v>
       </c>
-      <c r="C59" t="s">
-        <v>140</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="G59" t="s">
         <v>219</v>
-      </c>
-      <c r="F59" t="s">
-        <v>220</v>
-      </c>
-      <c r="G59" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3057,22 +3061,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>220</v>
+      </c>
+      <c r="C60" t="s">
+        <v>138</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60" t="s">
+        <v>221</v>
+      </c>
+      <c r="F60" t="s">
         <v>222</v>
       </c>
-      <c r="C60" t="s">
-        <v>140</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>223</v>
-      </c>
-      <c r="F60" t="s">
-        <v>224</v>
-      </c>
-      <c r="G60" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3080,22 +3084,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>224</v>
+      </c>
+      <c r="C61" t="s">
+        <v>138</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>225</v>
+      </c>
+      <c r="F61" t="s">
         <v>226</v>
       </c>
-      <c r="C61" t="s">
-        <v>140</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="G61" t="s">
         <v>227</v>
-      </c>
-      <c r="F61" t="s">
-        <v>228</v>
-      </c>
-      <c r="G61" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3103,22 +3107,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>228</v>
+      </c>
+      <c r="C62" t="s">
+        <v>229</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
         <v>230</v>
       </c>
-      <c r="C62" t="s">
+      <c r="F62" t="s">
         <v>231</v>
       </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>232</v>
-      </c>
-      <c r="F62" t="s">
-        <v>233</v>
-      </c>
-      <c r="G62" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3126,10 +3130,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C63" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -3138,10 +3142,10 @@
         <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G63" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3149,7 +3153,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C64" t="s">
         <v>7</v>
@@ -3158,13 +3162,13 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3172,7 +3176,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
@@ -3181,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F65" t="s">
         <v>17</v>
@@ -3195,22 +3199,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>240</v>
+      </c>
+      <c r="C66" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>240</v>
+      </c>
+      <c r="F66" t="s">
         <v>242</v>
       </c>
-      <c r="C66" t="s">
-        <v>243</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>242</v>
-      </c>
-      <c r="F66" t="s">
-        <v>244</v>
-      </c>
-      <c r="G66" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3218,7 +3222,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C67" t="s">
         <v>7</v>
@@ -3227,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F67" t="s">
         <v>9</v>
@@ -3238,19 +3242,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>245</v>
+      </c>
+      <c r="C68" t="s">
+        <v>246</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
         <v>247</v>
       </c>
-      <c r="C68" t="s">
+      <c r="F68" t="s">
         <v>248</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68" t="s">
-        <v>249</v>
-      </c>
-      <c r="F68" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3258,19 +3262,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>249</v>
+      </c>
+      <c r="C69" t="s">
+        <v>250</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
         <v>251</v>
       </c>
-      <c r="C69" t="s">
+      <c r="F69" t="s">
         <v>252</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69" t="s">
-        <v>253</v>
-      </c>
-      <c r="F69" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3278,19 +3282,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>253</v>
+      </c>
+      <c r="C70" t="s">
+        <v>254</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
         <v>255</v>
       </c>
-      <c r="C70" t="s">
+      <c r="F70" t="s">
         <v>256</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70" t="s">
-        <v>257</v>
-      </c>
-      <c r="F70" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3298,22 +3302,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>257</v>
+      </c>
+      <c r="C71" t="s">
+        <v>258</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
         <v>259</v>
       </c>
-      <c r="C71" t="s">
+      <c r="F71" t="s">
         <v>260</v>
       </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="G71" t="s">
         <v>261</v>
-      </c>
-      <c r="F71" t="s">
-        <v>262</v>
-      </c>
-      <c r="G71" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3321,19 +3325,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C72" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D72">
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F72" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3341,22 +3345,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>266</v>
+      </c>
+      <c r="C73" t="s">
+        <v>267</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
         <v>268</v>
       </c>
-      <c r="C73" t="s">
+      <c r="F73" t="s">
         <v>269</v>
       </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>270</v>
-      </c>
-      <c r="F73" t="s">
-        <v>271</v>
-      </c>
-      <c r="G73" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3364,22 +3368,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>271</v>
+      </c>
+      <c r="C74" t="s">
+        <v>272</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
         <v>273</v>
       </c>
-      <c r="C74" t="s">
+      <c r="F74" t="s">
         <v>274</v>
       </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>275</v>
-      </c>
-      <c r="F74" t="s">
-        <v>276</v>
-      </c>
-      <c r="G74" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">

--- a/LV_Regulator/LV_Regulator/Manufacture/LV_Regulator_BoM.xlsx
+++ b/LV_Regulator/LV_Regulator/Manufacture/LV_Regulator_BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pyonier\Documents\GitHub\LVPSU\LV_Regulator\LV_Regulator\Manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E079B17-3171-4FE8-9732-F7D74E03EC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AFD552-4BD1-4496-B484-AE5F5915FC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B4049184-6425-4836-AF0C-0336DDFBEC93}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B4049184-6425-4836-AF0C-0336DDFBEC93}"/>
   </bookViews>
   <sheets>
     <sheet name="LV_Regulator" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="284">
   <si>
     <t>Id</t>
   </si>
@@ -748,9 +748,6 @@
     <t>PinHeader_1x04_P2.54mm_Vertical</t>
   </si>
   <si>
-    <t>locally sourced</t>
-  </si>
-  <si>
     <t>TX</t>
   </si>
   <si>
@@ -854,13 +851,34 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/eaton-electronics-division/EHBSA080M5601010T/26408296?s=N4IgTCBcDaIKIAkBCBlAggBgBwYLIFYA2DARlIwBUQBdAXyA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/826646-2/2276168</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/TE-Connectivity/826646-2?qs=6Tj7fpyCzVqaIPUaVSFNTg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Microchip-Technology/25CSM04T-I-SN?qs=W%2FMpXkg%252BdQ4COJ43XO1dvg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Analog-Devices/ADM2483BRWZ-REEL?qs=BpaRKvA4VqG%252BMd7ITKpptQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Kingbright/APT3216YC?qs=fKJLI%2FsxXOfMof1%252BHeqe1A%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/STMicroelectronics/STM32F103C8T6?qs=bhCVus9SdFtq6kqxsU5%2FDA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://elektroleum.rs/proizvod/finder-41-52-9-005-0010-pcb-relej-5-v-dc-8-a-2-prekidac/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -991,6 +1009,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1293,7 +1319,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1336,12 +1362,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1375,6 +1403,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1696,13 +1725,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9665A2A8-71E5-4C81-B45D-479E88EB3CEB}">
   <dimension ref="A1:G83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="161.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="161.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="136" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1722,7 +1755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1745,7 +1778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1768,7 +1801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1791,7 +1824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1814,7 +1847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1837,7 +1870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1860,7 +1893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1883,7 +1916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1906,7 +1939,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1929,7 +1962,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1952,7 +1985,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1975,7 +2008,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1998,7 +2031,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2021,7 +2054,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2044,7 +2077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2067,7 +2100,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2090,7 +2123,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2107,13 +2140,13 @@
         <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G18" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2136,7 +2169,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2159,7 +2192,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2182,7 +2215,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2205,7 +2238,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2228,7 +2261,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2251,7 +2284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2274,7 +2307,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2297,7 +2330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2320,7 +2353,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2343,7 +2376,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2366,7 +2399,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2389,7 +2422,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2412,7 +2445,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2435,7 +2468,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2458,7 +2491,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2475,13 +2508,13 @@
         <v>123</v>
       </c>
       <c r="F34" t="s">
-        <v>124</v>
+        <v>283</v>
       </c>
       <c r="G34" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2504,7 +2537,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2527,7 +2560,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2550,7 +2583,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2573,7 +2606,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2596,7 +2629,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2619,7 +2652,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2642,7 +2675,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2665,7 +2698,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2688,7 +2721,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2711,7 +2744,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2734,7 +2767,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2757,7 +2790,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2780,7 +2813,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2803,7 +2836,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2826,7 +2859,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2849,7 +2882,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2872,7 +2905,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2895,7 +2928,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2918,7 +2951,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2941,7 +2974,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2964,7 +2997,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2987,7 +3020,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3010,7 +3043,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3033,7 +3066,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3056,7 +3089,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3079,7 +3112,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3102,7 +3135,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3125,7 +3158,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3148,7 +3181,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3171,7 +3204,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3194,7 +3227,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3210,19 +3243,19 @@
       <c r="E66" t="s">
         <v>240</v>
       </c>
-      <c r="F66" t="s">
-        <v>242</v>
-      </c>
-      <c r="G66" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F66" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C67" t="s">
         <v>7</v>
@@ -3231,207 +3264,224 @@
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G67" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" t="s">
         <v>245</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
         <v>246</v>
       </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>247</v>
       </c>
-      <c r="F68" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>248</v>
+      </c>
+      <c r="C69" t="s">
         <v>249</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
         <v>250</v>
       </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F69" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F69" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G69" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>252</v>
+      </c>
+      <c r="C70" t="s">
         <v>253</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
         <v>254</v>
       </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>255</v>
       </c>
-      <c r="F70" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G70" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>256</v>
+      </c>
+      <c r="C71" t="s">
         <v>257</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
         <v>258</v>
       </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>259</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>260</v>
       </c>
-      <c r="G71" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" t="s">
         <v>262</v>
-      </c>
-      <c r="C72" t="s">
-        <v>263</v>
       </c>
       <c r="D72">
         <v>4</v>
       </c>
       <c r="E72" t="s">
+        <v>263</v>
+      </c>
+      <c r="F72" t="s">
         <v>264</v>
       </c>
-      <c r="F72" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>265</v>
+      </c>
+      <c r="C73" t="s">
         <v>266</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
         <v>267</v>
       </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>268</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>269</v>
       </c>
-      <c r="G73" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>270</v>
+      </c>
+      <c r="C74" t="s">
         <v>271</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
         <v>272</v>
       </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>273</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>274</v>
       </c>
-      <c r="G74" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F66" r:id="rId1" xr:uid="{B7281884-6713-4913-B78E-9C462F0FFC0E}"/>
+    <hyperlink ref="G66" r:id="rId2" xr:uid="{E6F57BFD-38D7-4E9F-B7B9-816C3D732264}"/>
+    <hyperlink ref="F69" r:id="rId3" xr:uid="{B9541106-A655-41EF-A952-286553684825}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/LV_Regulator/LV_Regulator/Manufacture/LV_Regulator_BoM.xlsx
+++ b/LV_Regulator/LV_Regulator/Manufacture/LV_Regulator_BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pyonier\Documents\GitHub\LVPSU\LV_Regulator\LV_Regulator\Manufacture\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikola\Desktop\FS\LVPSU\LV_Regulator\LV_Regulator\Manufacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AFD552-4BD1-4496-B484-AE5F5915FC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7E9BC2-557E-4F79-89B4-5E7762DCAD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B4049184-6425-4836-AF0C-0336DDFBEC93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B4049184-6425-4836-AF0C-0336DDFBEC93}"/>
   </bookViews>
   <sheets>
     <sheet name="LV_Regulator" sheetId="1" r:id="rId1"/>
@@ -130,9 +130,6 @@
     <t>47uF</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/taiyo-yuden/MLASJ319LB5476MTNA01/16660604?s=N4IgTCBcDaILIBkCCBlAUgZgIwE4ECEBWAFgHYA2OAFQDkkAGLEAXQF8g</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/TAIYO-YUDEN/MLASJ319LB5476MTNA01?qs=tlsG%2FOw5FFj12GZbAd1Q9Q%3D%3D</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
     <t>22uF</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/murata-electronics/GGM31CD70J226KE02L/26264587?s=N4IgTCBcDaIOJwLIGYCMBhAIgdgAwCkwwA2AaQFFcwAZEAXQF8g</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/Murata-Electronics/GGM31CD70J226KE02L?qs=efUn273yAheMi1mARkgjog%3D%3D</t>
   </si>
   <si>
@@ -154,9 +148,6 @@
     <t>8pF</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/walsin-technology-corporation/1206N8R0B500CT/15989172?s=N4IgTCBcDaIIxgAwDYByAOASogQgVkUQGEAVEAXQF8g</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/Walsin/1206N8R0B500CT?qs=ZrPdAQfJ6DNlIoaP9IseAQ%3D%3D</t>
   </si>
   <si>
@@ -184,9 +175,6 @@
     <t>4.7uF</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/walsin-technology-corporation/SH31B475K250CT/15986750?s=N4IgTCBcDaIMoAkDMBGAQgFgOwFYDSYOADAMIAqIAugL5A</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/Walsin/SH31B475K250CT?qs=sGAEpiMZZMsh%252B1woXyUXjwgBgA0GYurkOe2xTrHbFqI%3D</t>
   </si>
   <si>
@@ -196,9 +184,6 @@
     <t>1uF</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/kemet/c1206c105k1rac7210/18116288</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/KEMET/C1206C105K1RAC7210?qs=u4fy%2FsgLU9Mgl3I%252Br1mPaw%3D%3D</t>
   </si>
   <si>
@@ -451,18 +436,12 @@
     <t>R2</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/ar1206jr-07120rl/5905688</t>
-  </si>
-  <si>
     <t>R4</t>
   </si>
   <si>
     <t>4k7</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/re1206dre074k7l/5924079</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/YAGEO/RE1206DRE074K7L?qs=sGAEpiMZZMtlubZbdhIBIKm0gsRX2fVkj2duGOZmAAU%3D</t>
   </si>
   <si>
@@ -604,9 +583,6 @@
     <t>57k</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/koa-speer-electronics-inc/RN73H2BTTD5762B50/10102553?s=N4IgTCBcDaIEoDkDsBmAEmAQgFWwEQFYkA2LAgBhAF0BfIA</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/KOA-Speer/RN73H2BTTD5762B50?qs=rI7uf1IzohRjg5ImrTOTZw%3D%3D</t>
   </si>
   <si>
@@ -616,9 +592,6 @@
     <t>1M</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/koa-speer-electronics-inc/rk73g2brttd1004f/16963535</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/KOA-Speer/RK73G2BRTTD1004F?qs=sGAEpiMZZMtlubZbdhIBIPTwcdbU5mXWvjZwu4hi2lQ%3D</t>
   </si>
   <si>
@@ -628,9 +601,6 @@
     <t>115k</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/koa-speer-electronics-inc/rn73h2bttd1153f100/10091376</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/KOA-Speer/RN73H2BTTD1153F100?qs=egkD4cx1ihRrPVr9m6Kwpw%3D%3D</t>
   </si>
   <si>
@@ -652,9 +622,6 @@
     <t>22k</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/koa-speer-electronics-inc/rn73h2bttd2202f100/10095657</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/KOA-Speer/RN73H2BTTD2202F100?qs=egkD4cx1ihQzyZ5aSCTtGw%3D%3D</t>
   </si>
   <si>
@@ -673,12 +640,6 @@
     <t>R38</t>
   </si>
   <si>
-    <t>50k</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/koa-speer-electronics-inc/rn73r2bttd3002b25/10045736</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/KOA-Speer/RN73R2BTTD5002B25?qs=2WXlatMagcHXnQ1HwYzmYA%3D%3D</t>
   </si>
   <si>
@@ -700,9 +661,6 @@
     <t>2.2k</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/panasonic-industry/ERA-8AED222V/19245472</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/Panasonic/ERA-8AED222V?qs=MNPzkKEzRtQm0146O%252BqXeg%3D%3D</t>
   </si>
   <si>
@@ -826,9 +784,6 @@
     <t>32.768kHz</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/seiko-instruments/sc32a-7pf20ppm/29480651</t>
-  </si>
-  <si>
     <t>https://eu.mouser.com/ProductDetail/Seiko-Instruments/SC32A-6PF20PPM?qs=Imq1NPwxi76SI853puRy%252Bw%3D%3D</t>
   </si>
   <si>
@@ -872,6 +827,51 @@
   </si>
   <si>
     <t>https://elektroleum.rs/proizvod/finder-41-52-9-005-0010-pcb-relej-5-v-dc-8-a-2-prekidac/</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/taiyo-yuden/MSASJ319LB5476MTNA01/22215176</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/murata-electronics/GCM31CD70J226KE02K/19115941</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cal-chip-electronics-inc/GMC31CG8R0C50NT/25975036</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/seiko-instruments/SC32S-7PF20PPM/4931504</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL31B475KAHNNNE/3886713</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cal-chip-electronics-inc/GMT31X7R105K100NT2/26921703</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/AC1206FR-07120RL/6006659</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC1206DR-074K7L/5919134</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RT1206FRD0722KL/21768884</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-passive-product/CRG1206F1M0/2380979</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/panasonic-industry/ERA-8AEB5762V/3071099</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC1206FR-07115KL/728512</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RT1206DRE072K2L/1082537</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RT1206BRD0730KL/1079730</t>
+  </si>
+  <si>
+    <t>30k</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1022,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1202,6 +1202,24 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1364,10 +1382,14 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="42" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="18" fillId="35" borderId="0" xfId="42" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1428,9 +1450,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1468,7 +1490,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1574,7 +1596,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1716,7 +1738,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1725,17 +1747,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9665A2A8-71E5-4C81-B45D-479E88EB3CEB}">
   <dimension ref="A1:G83"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="161.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="161.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="136" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1755,7 +1777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1765,20 +1787,20 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1788,20 +1810,20 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1811,20 +1833,20 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1834,20 +1856,20 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1857,20 +1879,20 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1880,20 +1902,20 @@
       <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1903,20 +1925,20 @@
       <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>9</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1926,20 +1948,20 @@
       <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>3</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1949,20 +1971,20 @@
       <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>5</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1972,531 +1994,531 @@
       <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="4">
         <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>35</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="4">
         <v>2</v>
       </c>
       <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="4">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15">
+        <v>48</v>
+      </c>
+      <c r="D15" s="4">
         <v>4</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17">
+        <v>48</v>
+      </c>
+      <c r="D17" s="4">
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18">
+        <v>56</v>
+      </c>
+      <c r="D18" s="4">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" t="s">
-        <v>276</v>
-      </c>
-      <c r="G18" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19">
+        <v>59</v>
+      </c>
+      <c r="D19" s="4">
         <v>2</v>
       </c>
       <c r="E19" t="s">
         <v>35</v>
       </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20">
+        <v>56</v>
+      </c>
+      <c r="D20" s="4">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21">
+        <v>67</v>
+      </c>
+      <c r="D21" s="4">
         <v>2</v>
       </c>
       <c r="E21">
         <v>430450400</v>
       </c>
-      <c r="F21" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22">
+        <v>71</v>
+      </c>
+      <c r="D22" s="4">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23">
+        <v>76</v>
+      </c>
+      <c r="D23" s="4">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24">
+        <v>71</v>
+      </c>
+      <c r="D24" s="4">
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25">
+        <v>83</v>
+      </c>
+      <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25">
         <v>2169890001</v>
       </c>
-      <c r="F25" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="4">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27">
+        <v>89</v>
+      </c>
+      <c r="D27" s="4">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
         <v>94</v>
       </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29">
+        <v>89</v>
+      </c>
+      <c r="D29" s="4">
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" t="s">
-        <v>104</v>
-      </c>
-      <c r="G29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30">
+        <v>102</v>
+      </c>
+      <c r="D30" s="4">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" t="s">
-        <v>109</v>
-      </c>
-      <c r="G30" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31">
+        <v>107</v>
+      </c>
+      <c r="D31" s="4">
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
-      </c>
-      <c r="F31" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32">
+        <v>111</v>
+      </c>
+      <c r="D32" s="4">
         <v>2</v>
       </c>
       <c r="E32">
         <v>430450800</v>
       </c>
-      <c r="F32" t="s">
-        <v>117</v>
-      </c>
-      <c r="G32" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="4">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C34" s="1">
         <v>415000000000</v>
@@ -2505,973 +2527,974 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
-      </c>
-      <c r="F34" t="s">
-        <v>283</v>
-      </c>
-      <c r="G34" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35">
+        <v>121</v>
+      </c>
+      <c r="D35" s="4">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>127</v>
-      </c>
-      <c r="F35" t="s">
-        <v>128</v>
-      </c>
-      <c r="G35" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="4">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
-      </c>
-      <c r="F36" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37">
+        <v>128</v>
+      </c>
+      <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>134</v>
-      </c>
-      <c r="F37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G37" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38">
+        <v>133</v>
+      </c>
+      <c r="D38" s="5">
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>139</v>
-      </c>
-      <c r="F38" t="s">
-        <v>140</v>
-      </c>
-      <c r="G38" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39">
+        <v>133</v>
+      </c>
+      <c r="D39" s="4">
         <v>1</v>
       </c>
       <c r="E39">
         <v>120</v>
       </c>
-      <c r="F39" t="s">
-        <v>143</v>
-      </c>
-      <c r="G39" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F39" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
-      </c>
-      <c r="D40">
+        <v>133</v>
+      </c>
+      <c r="D40" s="4">
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>145</v>
-      </c>
-      <c r="F40" t="s">
-        <v>146</v>
-      </c>
-      <c r="G40" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
-      </c>
-      <c r="D41">
+        <v>133</v>
+      </c>
+      <c r="D41" s="4">
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F41" t="s">
-        <v>150</v>
-      </c>
-      <c r="G41" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42">
+        <v>133</v>
+      </c>
+      <c r="D42" s="4">
         <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>153</v>
-      </c>
-      <c r="F42" t="s">
-        <v>154</v>
-      </c>
-      <c r="G42" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
-      </c>
-      <c r="D43">
+        <v>133</v>
+      </c>
+      <c r="D43" s="4">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>157</v>
-      </c>
-      <c r="F43" t="s">
-        <v>158</v>
-      </c>
-      <c r="G43" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
-      </c>
-      <c r="D44">
+        <v>133</v>
+      </c>
+      <c r="D44" s="4">
         <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>161</v>
-      </c>
-      <c r="F44" t="s">
         <v>154</v>
       </c>
-      <c r="G44" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F44" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45">
+        <v>133</v>
+      </c>
+      <c r="D45" s="4">
         <v>3</v>
       </c>
       <c r="E45">
         <v>270</v>
       </c>
-      <c r="F45" t="s">
-        <v>163</v>
-      </c>
-      <c r="G45" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F45" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
-      </c>
-      <c r="D46">
+        <v>133</v>
+      </c>
+      <c r="D46" s="4">
         <v>9</v>
       </c>
       <c r="E46">
         <v>130</v>
       </c>
-      <c r="F46" t="s">
-        <v>166</v>
-      </c>
-      <c r="G46" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F46" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47">
+        <v>133</v>
+      </c>
+      <c r="D47" s="4">
         <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>169</v>
-      </c>
-      <c r="F47" t="s">
-        <v>170</v>
-      </c>
-      <c r="G47" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
-      </c>
-      <c r="D48">
+        <v>133</v>
+      </c>
+      <c r="D48" s="5">
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>173</v>
-      </c>
-      <c r="F48" t="s">
-        <v>174</v>
-      </c>
-      <c r="G48" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
-      </c>
-      <c r="D49">
+        <v>133</v>
+      </c>
+      <c r="D49" s="4">
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>177</v>
-      </c>
-      <c r="F49" t="s">
-        <v>178</v>
-      </c>
-      <c r="G49" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
-      </c>
-      <c r="D50">
+        <v>133</v>
+      </c>
+      <c r="D50" s="5">
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>181</v>
-      </c>
-      <c r="F50" t="s">
-        <v>182</v>
-      </c>
-      <c r="G50" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
-      </c>
-      <c r="D51">
+        <v>133</v>
+      </c>
+      <c r="D51" s="4">
         <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>185</v>
-      </c>
-      <c r="F51" t="s">
-        <v>186</v>
-      </c>
-      <c r="G51" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
-      </c>
-      <c r="D52">
+        <v>133</v>
+      </c>
+      <c r="D52" s="4">
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>189</v>
-      </c>
-      <c r="F52" t="s">
-        <v>190</v>
-      </c>
-      <c r="G52" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
-      </c>
-      <c r="D53">
+        <v>133</v>
+      </c>
+      <c r="D53" s="4">
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>193</v>
-      </c>
-      <c r="F53" t="s">
-        <v>194</v>
-      </c>
-      <c r="G53" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
-      </c>
-      <c r="D54">
+        <v>133</v>
+      </c>
+      <c r="D54" s="4">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>197</v>
-      </c>
-      <c r="F54" t="s">
-        <v>198</v>
-      </c>
-      <c r="G54" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
-      </c>
-      <c r="D55">
+        <v>133</v>
+      </c>
+      <c r="D55" s="4">
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>201</v>
-      </c>
-      <c r="F55" t="s">
-        <v>202</v>
-      </c>
-      <c r="G55" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
-      </c>
-      <c r="D56">
+        <v>133</v>
+      </c>
+      <c r="D56" s="4">
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>205</v>
-      </c>
-      <c r="F56" t="s">
-        <v>206</v>
-      </c>
-      <c r="G56" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
-      </c>
-      <c r="D57">
+        <v>133</v>
+      </c>
+      <c r="D57" s="4">
         <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>209</v>
-      </c>
-      <c r="F57" t="s">
-        <v>210</v>
-      </c>
-      <c r="G57" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>213</v>
-      </c>
-      <c r="F58" t="s">
-        <v>214</v>
-      </c>
-      <c r="G58" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
-      </c>
-      <c r="D59">
+        <v>133</v>
+      </c>
+      <c r="D59" s="4">
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>217</v>
-      </c>
-      <c r="F59" t="s">
-        <v>218</v>
-      </c>
-      <c r="G59" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
-      </c>
-      <c r="D60">
+        <v>133</v>
+      </c>
+      <c r="D60" s="4">
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>221</v>
-      </c>
-      <c r="F60" t="s">
-        <v>222</v>
-      </c>
-      <c r="G60" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61">
+        <v>133</v>
+      </c>
+      <c r="D61" s="4">
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>225</v>
-      </c>
-      <c r="F61" t="s">
-        <v>226</v>
-      </c>
-      <c r="G61" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C62" t="s">
-        <v>229</v>
-      </c>
-      <c r="D62">
+        <v>215</v>
+      </c>
+      <c r="D62" s="4">
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>230</v>
-      </c>
-      <c r="F62" t="s">
-        <v>231</v>
-      </c>
-      <c r="G62" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
-      </c>
-      <c r="D63">
+        <v>133</v>
+      </c>
+      <c r="D63" s="4">
         <v>2</v>
       </c>
       <c r="E63">
         <v>10</v>
       </c>
-      <c r="F63" t="s">
-        <v>234</v>
-      </c>
-      <c r="G63" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F63" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="C64" t="s">
         <v>7</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="4">
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>237</v>
-      </c>
-      <c r="F64" t="s">
-        <v>121</v>
-      </c>
-      <c r="G64" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="4">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>239</v>
-      </c>
-      <c r="F65" t="s">
+        <v>225</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
-      </c>
-      <c r="D66">
+        <v>227</v>
+      </c>
+      <c r="D66" s="5">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C67" t="s">
         <v>7</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="4">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>243</v>
-      </c>
-      <c r="F67" t="s">
+        <v>229</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G67" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G67" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C68" t="s">
-        <v>245</v>
-      </c>
-      <c r="D68">
+        <v>231</v>
+      </c>
+      <c r="D68" s="4">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>246</v>
-      </c>
-      <c r="F68" t="s">
-        <v>247</v>
-      </c>
-      <c r="G68" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C69" t="s">
-        <v>249</v>
-      </c>
-      <c r="D69">
+        <v>235</v>
+      </c>
+      <c r="D69" s="4">
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="G69" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C70" t="s">
-        <v>253</v>
-      </c>
-      <c r="D70">
+        <v>239</v>
+      </c>
+      <c r="D70" s="4">
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>254</v>
-      </c>
-      <c r="F70" t="s">
-        <v>255</v>
-      </c>
-      <c r="G70" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C71" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>258</v>
-      </c>
-      <c r="F71" t="s">
-        <v>259</v>
-      </c>
-      <c r="G71" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
-      </c>
-      <c r="D72">
+        <v>248</v>
+      </c>
+      <c r="D72" s="4">
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>263</v>
-      </c>
-      <c r="F72" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G72" s="3"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C73" t="s">
-        <v>266</v>
-      </c>
-      <c r="D73">
+        <v>252</v>
+      </c>
+      <c r="D73" s="4">
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>267</v>
-      </c>
-      <c r="F73" t="s">
-        <v>268</v>
-      </c>
-      <c r="G73" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C74" t="s">
-        <v>271</v>
-      </c>
-      <c r="D74">
+        <v>256</v>
+      </c>
+      <c r="D74" s="4">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>272</v>
-      </c>
-      <c r="F74" t="s">
-        <v>273</v>
-      </c>
-      <c r="G74" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3481,7 +3504,67 @@
     <hyperlink ref="F66" r:id="rId1" xr:uid="{B7281884-6713-4913-B78E-9C462F0FFC0E}"/>
     <hyperlink ref="G66" r:id="rId2" xr:uid="{E6F57BFD-38D7-4E9F-B7B9-816C3D732264}"/>
     <hyperlink ref="F69" r:id="rId3" xr:uid="{B9541106-A655-41EF-A952-286553684825}"/>
+    <hyperlink ref="F2" r:id="rId4" xr:uid="{53351313-884C-4239-84DA-903C62D38650}"/>
+    <hyperlink ref="F3" r:id="rId5" xr:uid="{C32D8DF4-7258-40BE-8C12-C016595F03A3}"/>
+    <hyperlink ref="F4" r:id="rId6" xr:uid="{257FC3B0-383D-4228-AD13-21009FBDB1A6}"/>
+    <hyperlink ref="F65" r:id="rId7" xr:uid="{1288B427-D32B-4B99-956C-1D8F5C34A100}"/>
+    <hyperlink ref="F36" r:id="rId8" xr:uid="{863BEF7C-22D1-4370-B106-E6796EBECD27}"/>
+    <hyperlink ref="F8" r:id="rId9" xr:uid="{E7BC18B3-13E2-40A8-83EF-B4745034053E}"/>
+    <hyperlink ref="F9" r:id="rId10" xr:uid="{56F7C012-05AB-4E37-9A5C-E698E1525C6C}"/>
+    <hyperlink ref="F10" r:id="rId11" xr:uid="{06A9DAC2-DC85-4F5E-8E1D-BFDF534A7760}"/>
+    <hyperlink ref="F11" r:id="rId12" xr:uid="{2EAB4CC9-1486-48F8-B621-DFF5629DED5F}"/>
+    <hyperlink ref="F12" r:id="rId13" xr:uid="{79D34DC3-E229-493B-AF95-83A87ABEB389}"/>
+    <hyperlink ref="F13" r:id="rId14" xr:uid="{5745E83C-247C-4BB4-B2F9-D8110641FC5D}"/>
+    <hyperlink ref="F14" r:id="rId15" xr:uid="{1D8A608E-2FAA-49B9-BA8B-B352B21797AF}"/>
+    <hyperlink ref="F21" r:id="rId16" xr:uid="{B7992817-316D-4F7B-BF43-D68D70386926}"/>
+    <hyperlink ref="F22" r:id="rId17" xr:uid="{6FF3F080-7164-4A21-9C43-A3E19F709B66}"/>
+    <hyperlink ref="F23" r:id="rId18" xr:uid="{F7E22167-9F86-46C4-A28A-02A2788DC7D2}"/>
+    <hyperlink ref="F25" r:id="rId19" xr:uid="{37A82DD2-FB9B-4BC6-BDE9-C5665FF98A98}"/>
+    <hyperlink ref="F72" r:id="rId20" xr:uid="{486F7077-EEEE-4862-A9EB-483EB0D552E0}"/>
+    <hyperlink ref="F32" r:id="rId21" xr:uid="{E0109888-D97E-4FA6-BA9F-AC6FB3629753}"/>
+    <hyperlink ref="F35" r:id="rId22" xr:uid="{66F7BEE3-F95F-4DC2-A00B-64657520F060}"/>
+    <hyperlink ref="F31" r:id="rId23" xr:uid="{DD6C1172-4B9C-4771-9BA1-60101AD5B049}"/>
+    <hyperlink ref="F37" r:id="rId24" xr:uid="{5B5D86A6-129C-4170-A420-BAB715F6A195}"/>
+    <hyperlink ref="F30" r:id="rId25" xr:uid="{E4E54EFF-7124-4F22-BC02-D7E0E130E89F}"/>
+    <hyperlink ref="F71" r:id="rId26" xr:uid="{FAA66DD0-C932-4DB6-9A6E-402566E89254}"/>
+    <hyperlink ref="F70" r:id="rId27" xr:uid="{925709E6-3BC0-4908-B87A-9AC8F9100A21}"/>
+    <hyperlink ref="F68" r:id="rId28" xr:uid="{BC6DF213-4D0C-4D42-B56C-987ADAF89318}"/>
+    <hyperlink ref="F73" r:id="rId29" xr:uid="{6CF57B2C-E011-495F-B197-0D8C51BCC777}"/>
+    <hyperlink ref="F74" r:id="rId30" xr:uid="{ADBCFA0E-6294-4330-A6B1-9593339EC4C3}"/>
+    <hyperlink ref="F16" r:id="rId31" xr:uid="{1C188C0D-1BEC-499B-9F2E-4E2CD46A9920}"/>
+    <hyperlink ref="F17" r:id="rId32" xr:uid="{00694C44-A6DE-4907-B2AD-FECA05D13D17}"/>
+    <hyperlink ref="F18" r:id="rId33" xr:uid="{6D5061A1-65C3-4DEC-AAC3-677120F47D92}"/>
+    <hyperlink ref="F19" r:id="rId34" xr:uid="{A2DCDEED-8EA7-4495-BB0A-0162BAF8BE3B}"/>
+    <hyperlink ref="F20" r:id="rId35" xr:uid="{01D4C19A-E4F9-4FF4-B626-C67DB994BDDD}"/>
+    <hyperlink ref="F27" r:id="rId36" xr:uid="{E08C817F-75EE-4880-93E7-22251EA5E237}"/>
+    <hyperlink ref="F28" r:id="rId37" xr:uid="{78B12C9A-A969-4877-8AE4-19EDC198D1AE}"/>
+    <hyperlink ref="F29" r:id="rId38" xr:uid="{7E3F85C3-0B4A-45DC-8F31-A1E460CA912F}"/>
+    <hyperlink ref="F39" r:id="rId39" xr:uid="{CE65B27C-BD2F-4B0E-9292-E766B003FBC7}"/>
+    <hyperlink ref="F40" r:id="rId40" xr:uid="{6DFEA32F-7950-4FA4-86CF-80BD49CC34FB}"/>
+    <hyperlink ref="F41" r:id="rId41" xr:uid="{370B0B78-AEEB-4C0A-88D5-5F7052692370}"/>
+    <hyperlink ref="F42" r:id="rId42" xr:uid="{1626CB67-F72F-4C21-BD8A-1BF8068C6FE9}"/>
+    <hyperlink ref="F43" r:id="rId43" xr:uid="{E406DE65-8417-4F62-9CF4-CB3600D418A3}"/>
+    <hyperlink ref="F62" r:id="rId44" xr:uid="{51E6F5D7-099D-4B71-8CC7-E2DE614A4B57}"/>
+    <hyperlink ref="F63" r:id="rId45" xr:uid="{DF81F636-FE9B-445F-A124-622DDB1403D0}"/>
+    <hyperlink ref="F46" r:id="rId46" xr:uid="{3ED2874C-EDAF-4D03-B4DD-58B27B0F9CF7}"/>
+    <hyperlink ref="F45" r:id="rId47" xr:uid="{A293AE74-A5A1-409E-A42B-A51CDD559E30}"/>
+    <hyperlink ref="F47" r:id="rId48" xr:uid="{75C90EB5-E6C1-4F0D-A3E2-7D229C52DD56}"/>
+    <hyperlink ref="F48" r:id="rId49" xr:uid="{76B3F081-BA15-4040-BBBD-A663817D7B43}"/>
+    <hyperlink ref="F49" r:id="rId50" xr:uid="{B8794B50-10E4-40F7-9D2E-297B4EEC0762}"/>
+    <hyperlink ref="F50" r:id="rId51" xr:uid="{2DC44F31-51B9-4502-84FA-04CC3F354D08}"/>
+    <hyperlink ref="F51" r:id="rId52" xr:uid="{5BB8DDB6-93E3-4302-9FAF-5C45F0C15E04}"/>
+    <hyperlink ref="F52" r:id="rId53" xr:uid="{4A9E9D06-EF2C-44EF-864D-03863C6B979D}"/>
+    <hyperlink ref="F57" r:id="rId54" xr:uid="{AC7408F8-65E9-4D24-8701-BE78E29E18F3}"/>
+    <hyperlink ref="F56" r:id="rId55" xr:uid="{989E19AE-AABB-4029-9093-A9825CDA8FBC}"/>
+    <hyperlink ref="F54" r:id="rId56" xr:uid="{F176140A-3F10-4D48-A1FA-38C99BBC20B6}"/>
+    <hyperlink ref="F53" r:id="rId57" xr:uid="{3FF7127F-1E9C-4000-9BD6-24345318446B}"/>
+    <hyperlink ref="F55" r:id="rId58" xr:uid="{DDE38FB3-B268-44E2-9A71-9C5157852E5E}"/>
+    <hyperlink ref="F61" r:id="rId59" xr:uid="{EF474BF4-DE3D-4DC9-A3BF-375D32D5E173}"/>
+    <hyperlink ref="F60" r:id="rId60" xr:uid="{F0F3F7CE-FE99-4161-B1C8-23B43383EF1E}"/>
+    <hyperlink ref="F59" r:id="rId61" xr:uid="{A6332B0C-ED02-468F-892B-1C58B7188FFF}"/>
+    <hyperlink ref="F58" r:id="rId62" xr:uid="{0C8C56D1-6099-4B0E-937A-DB9BA2394000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId63"/>
 </worksheet>
 </file>